--- a/Documents/Product Catalog/Living Room Furniture.xlsx
+++ b/Documents/Product Catalog/Living Room Furniture.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E0CEBD-E485-4CBE-9AED-7D4E0B842396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9768CFE1-ADBF-46BF-A0A5-08B45FEF1158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="162">
   <si>
     <t>Talukder Furniture Ltd.</t>
   </si>
@@ -204,9 +204,6 @@
   </si>
   <si>
     <t>TFL-DVN-203 FR</t>
-  </si>
-  <si>
-    <t>Sofa</t>
   </si>
   <si>
     <t>L 750 X 700 X 825 mm (Single Seater)</t>
@@ -787,6 +784,12 @@
   </si>
   <si>
     <t>Living Room</t>
+  </si>
+  <si>
+    <t>Single Seater Sofa</t>
+  </si>
+  <si>
+    <t>Double Seater Sofa</t>
   </si>
 </sst>
 </file>
@@ -4723,10 +4726,10 @@
         <v>12</v>
       </c>
       <c r="P3" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -4770,7 +4773,7 @@
         <v>14</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I4" s="27"/>
       <c r="J4" s="33"/>
@@ -4828,13 +4831,13 @@
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>50</v>
@@ -4856,16 +4859,16 @@
         <v>0.1</v>
       </c>
       <c r="N5" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="O5" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="O5" s="20" t="s">
+      <c r="P5" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="P5" s="19" t="s">
+      <c r="Q5" s="19" t="s">
         <v>104</v>
-      </c>
-      <c r="Q5" s="19" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -4880,13 +4883,13 @@
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>50</v>
@@ -4908,16 +4911,16 @@
         <v>0.1</v>
       </c>
       <c r="N6" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O6" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="P6" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="P6" s="19" t="s">
+      <c r="Q6" s="19" t="s">
         <v>104</v>
-      </c>
-      <c r="Q6" s="19" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -4932,13 +4935,13 @@
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>50</v>
@@ -4958,16 +4961,16 @@
         <v>0.1</v>
       </c>
       <c r="N7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="O7" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="O7" s="20" t="s">
+      <c r="P7" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="P7" s="19" t="s">
+      <c r="Q7" s="19" t="s">
         <v>130</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -4975,26 +4978,26 @@
         <v>22</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>48</v>
@@ -5010,16 +5013,16 @@
         <v>0.1</v>
       </c>
       <c r="N8" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="O8" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="O8" s="20" t="s">
+      <c r="P8" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="P8" s="19" t="s">
+      <c r="Q8" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="Q8" s="19" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -5027,26 +5030,26 @@
         <v>23</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>48</v>
@@ -5062,16 +5065,16 @@
         <v>0.1</v>
       </c>
       <c r="N9" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O9" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="P9" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="P9" s="19" t="s">
+      <c r="Q9" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="Q9" s="19" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -5079,26 +5082,26 @@
         <v>24</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>48</v>
@@ -5114,16 +5117,16 @@
         <v>0.1</v>
       </c>
       <c r="N10" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O10" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="P10" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="P10" s="19" t="s">
+      <c r="Q10" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="Q10" s="19" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -5131,26 +5134,26 @@
         <v>25</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>48</v>
@@ -5166,16 +5169,16 @@
         <v>0.1</v>
       </c>
       <c r="N11" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O11" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="P11" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="P11" s="19" t="s">
+      <c r="Q11" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -5183,26 +5186,26 @@
         <v>26</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>48</v>
@@ -5218,16 +5221,16 @@
         <v>0.1</v>
       </c>
       <c r="N12" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O12" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="P12" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="P12" s="19" t="s">
+      <c r="Q12" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="Q12" s="19" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -5235,26 +5238,26 @@
         <v>27</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>48</v>
@@ -5270,16 +5273,16 @@
         <v>0.1</v>
       </c>
       <c r="N13" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O13" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="P13" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="P13" s="19" t="s">
+      <c r="Q13" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="Q13" s="19" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -5287,26 +5290,26 @@
         <v>28</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>48</v>
@@ -5322,16 +5325,16 @@
         <v>0.1</v>
       </c>
       <c r="N14" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="O14" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="O14" s="20" t="s">
+      <c r="P14" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="P14" s="19" t="s">
-        <v>118</v>
-      </c>
       <c r="Q14" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -5339,26 +5342,26 @@
         <v>29</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>48</v>
@@ -5374,16 +5377,16 @@
         <v>0.1</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O15" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="P15" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="P15" s="19" t="s">
-        <v>118</v>
-      </c>
       <c r="Q15" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -5391,26 +5394,26 @@
         <v>30</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>48</v>
@@ -5426,16 +5429,16 @@
         <v>0.1</v>
       </c>
       <c r="N16" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="O16" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="O16" s="20" t="s">
+      <c r="P16" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="P16" s="19" t="s">
-        <v>122</v>
-      </c>
       <c r="Q16" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5443,26 +5446,26 @@
         <v>31</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>48</v>
@@ -5478,16 +5481,16 @@
         <v>0.1</v>
       </c>
       <c r="N17" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O17" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="P17" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="P17" s="19" t="s">
-        <v>122</v>
-      </c>
       <c r="Q17" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5495,26 +5498,26 @@
         <v>32</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>48</v>
@@ -5530,16 +5533,16 @@
         <v>0.1</v>
       </c>
       <c r="N18" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="O18" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="O18" s="20" t="s">
+      <c r="P18" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="P18" s="19" t="s">
-        <v>126</v>
-      </c>
       <c r="Q18" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5547,26 +5550,26 @@
         <v>33</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>48</v>
@@ -5582,16 +5585,16 @@
         <v>0.1</v>
       </c>
       <c r="N19" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O19" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="P19" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="P19" s="19" t="s">
-        <v>126</v>
-      </c>
       <c r="Q19" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5599,26 +5602,26 @@
         <v>34</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>68</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>48</v>
@@ -5634,16 +5637,16 @@
         <v>0.1</v>
       </c>
       <c r="N20" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="O20" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O20" s="20" t="s">
+      <c r="P20" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P20" s="19" t="s">
+      <c r="Q20" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q20" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5651,26 +5654,26 @@
         <v>35</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>48</v>
@@ -5686,16 +5689,16 @@
         <v>0.1</v>
       </c>
       <c r="N21" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O21" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P21" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P21" s="19" t="s">
+      <c r="Q21" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q21" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5703,26 +5706,26 @@
         <v>36</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>48</v>
@@ -5738,16 +5741,16 @@
         <v>0.1</v>
       </c>
       <c r="N22" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O22" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P22" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P22" s="19" t="s">
+      <c r="Q22" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q22" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5755,26 +5758,26 @@
         <v>37</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>48</v>
@@ -5790,16 +5793,16 @@
         <v>0.1</v>
       </c>
       <c r="N23" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="O23" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="O23" s="20" t="s">
+      <c r="P23" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="P23" s="19" t="s">
-        <v>99</v>
-      </c>
       <c r="Q23" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5807,26 +5810,26 @@
         <v>38</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>48</v>
@@ -5842,16 +5845,16 @@
         <v>0.1</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O24" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P24" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P24" s="19" t="s">
+      <c r="Q24" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q24" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5859,26 +5862,26 @@
         <v>39</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>48</v>
@@ -5894,16 +5897,16 @@
         <v>0.1</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O25" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P25" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P25" s="19" t="s">
+      <c r="Q25" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q25" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5911,26 +5914,26 @@
         <v>40</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D26" s="8"/>
       <c r="E26" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>48</v>
@@ -5946,16 +5949,16 @@
         <v>0.1</v>
       </c>
       <c r="N26" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="O26" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="O26" s="20" t="s">
+      <c r="P26" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="P26" s="19" t="s">
-        <v>99</v>
-      </c>
       <c r="Q26" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -5963,26 +5966,26 @@
         <v>41</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>48</v>
@@ -5998,16 +6001,16 @@
         <v>0.1</v>
       </c>
       <c r="N27" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O27" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P27" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P27" s="19" t="s">
+      <c r="Q27" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q27" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -6015,26 +6018,26 @@
         <v>42</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>48</v>
@@ -6050,16 +6053,16 @@
         <v>0.1</v>
       </c>
       <c r="N28" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O28" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P28" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P28" s="19" t="s">
+      <c r="Q28" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q28" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -6067,26 +6070,26 @@
         <v>43</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>48</v>
@@ -6102,16 +6105,16 @@
         <v>0.1</v>
       </c>
       <c r="N29" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="O29" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="O29" s="20" t="s">
+      <c r="P29" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P29" s="19" t="s">
+      <c r="Q29" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q29" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -6119,26 +6122,26 @@
         <v>44</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>48</v>
@@ -6154,16 +6157,16 @@
         <v>0.1</v>
       </c>
       <c r="N30" s="18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O30" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P30" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P30" s="19" t="s">
+      <c r="Q30" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q30" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -6171,26 +6174,26 @@
         <v>45</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>48</v>
@@ -6206,16 +6209,16 @@
         <v>0.1</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O31" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="P31" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="P31" s="19" t="s">
+      <c r="Q31" s="19" t="s">
         <v>93</v>
-      </c>
-      <c r="Q31" s="19" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="80.099999999999994" customHeight="1">
@@ -6223,29 +6226,29 @@
         <v>46</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>132</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>133</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I32" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="K32" s="12">
         <f>L32*(1-0.1)</f>
@@ -6258,16 +6261,16 @@
         <v>0.1</v>
       </c>
       <c r="N32" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="O32" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="O32" s="20" t="s">
+      <c r="P32" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="P32" s="19" t="s">
+      <c r="Q32" s="19" t="s">
         <v>139</v>
-      </c>
-      <c r="Q32" s="19" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:46" ht="80.099999999999994" customHeight="1">
@@ -6275,29 +6278,29 @@
         <v>47</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K33" s="12">
         <f>L33*(1-0.1)</f>
@@ -6310,16 +6313,16 @@
         <v>0.1</v>
       </c>
       <c r="N33" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="O33" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="O33" s="20" t="s">
+      <c r="P33" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="P33" s="19" t="s">
+      <c r="Q33" s="19" t="s">
         <v>139</v>
-      </c>
-      <c r="Q33" s="19" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:46" ht="80.099999999999994" customHeight="1">
